--- a/backend/data/financials_by_company/0509.HK.xlsx
+++ b/backend/data/financials_by_company/0509.HK.xlsx
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>774342</v>
+        <v>-3291896</v>
       </c>
       <c r="C2" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="D2" t="n">
-        <v>-279530000</v>
+        <v>-16339000</v>
       </c>
       <c r="E2" t="n">
-        <v>194135000</v>
+        <v>-822974000</v>
       </c>
       <c r="F2" t="n">
-        <v>43019000</v>
+        <v>-822974000</v>
       </c>
       <c r="G2" t="n">
-        <v>-236690000</v>
+        <v>-1121566000</v>
       </c>
       <c r="H2" t="n">
-        <v>219459000</v>
+        <v>220093000</v>
       </c>
       <c r="I2" t="n">
-        <v>395915000</v>
+        <v>1200336000</v>
       </c>
       <c r="J2" t="n">
-        <v>-85395000</v>
+        <v>-839313000</v>
       </c>
       <c r="K2" t="n">
-        <v>-304854000</v>
+        <v>-1059406000</v>
       </c>
       <c r="L2" t="n">
-        <v>-178045000</v>
+        <v>-198824000</v>
       </c>
       <c r="M2" t="n">
-        <v>178819000</v>
+        <v>200301000</v>
       </c>
       <c r="N2" t="n">
-        <v>774000</v>
+        <v>1477000</v>
       </c>
       <c r="O2" t="n">
-        <v>-127818658</v>
+        <v>-301883896</v>
       </c>
       <c r="P2" t="n">
-        <v>-236690000</v>
+        <v>-1121566000</v>
       </c>
       <c r="Q2" t="n">
-        <v>693716000</v>
+        <v>1586695000</v>
       </c>
       <c r="R2" t="n">
         <v>114527925</v>
@@ -719,89 +719,91 @@
         <v>114527925</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.984</v>
+        <v>-9.792</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.068</v>
+        <v>-9.792</v>
       </c>
       <c r="V2" t="n">
-        <v>-236690000</v>
+        <v>-1121566000</v>
       </c>
       <c r="W2" t="n">
-        <v>-236690000</v>
+        <v>-1121566000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-236690000</v>
+        <v>-1121566000</v>
       </c>
       <c r="Z2" t="n">
-        <v>238446000</v>
+        <v>132536000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-475136000</v>
+        <v>-1254102000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-475136000</v>
+        <v>-1254102000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-8537000</v>
+        <v>-5605000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-483673000</v>
+        <v>-1259707000</v>
       </c>
       <c r="AE2" t="n">
-        <v>5884000</v>
+        <v>7776000</v>
       </c>
       <c r="AF2" t="n">
-        <v>43982000</v>
+        <v>-830485000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-648911000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>-6577000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>173111000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>453813000</v>
+        <v>837062000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-178045000</v>
+        <v>-198824000</v>
       </c>
       <c r="AK2" t="n">
-        <v>178819000</v>
+        <v>200301000</v>
       </c>
       <c r="AL2" t="n">
-        <v>774000</v>
+        <v>1477000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-378134000</v>
+        <v>-254837000</v>
       </c>
       <c r="AN2" t="n">
-        <v>297801000</v>
+        <v>386359000</v>
       </c>
       <c r="AO2" t="n">
-        <v>29722000</v>
+        <v>173111000</v>
       </c>
       <c r="AP2" t="n">
-        <v>269411000</v>
+        <v>240190000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4728000</v>
+        <v>34377000</v>
       </c>
       <c r="AR2" t="n">
-        <v>264683000</v>
+        <v>205813000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-80333000</v>
+        <v>131522000</v>
       </c>
       <c r="AT2" t="n">
-        <v>395915000</v>
+        <v>1200336000</v>
       </c>
       <c r="AU2" t="n">
-        <v>315582000</v>
+        <v>1331858000</v>
       </c>
       <c r="AV2" t="n">
-        <v>315582000</v>
+        <v>1331858000</v>
       </c>
     </row>
     <row r="3">
@@ -950,55 +952,55 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-3291896</v>
+        <v>774342</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="D4" t="n">
-        <v>-16339000</v>
+        <v>-279530000</v>
       </c>
       <c r="E4" t="n">
-        <v>-822974000</v>
+        <v>194135000</v>
       </c>
       <c r="F4" t="n">
-        <v>-822974000</v>
+        <v>43019000</v>
       </c>
       <c r="G4" t="n">
-        <v>-1121566000</v>
+        <v>-236690000</v>
       </c>
       <c r="H4" t="n">
-        <v>220093000</v>
+        <v>219459000</v>
       </c>
       <c r="I4" t="n">
-        <v>1200336000</v>
+        <v>395915000</v>
       </c>
       <c r="J4" t="n">
-        <v>-839313000</v>
+        <v>-85395000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1059406000</v>
+        <v>-304854000</v>
       </c>
       <c r="L4" t="n">
-        <v>-198824000</v>
+        <v>-178045000</v>
       </c>
       <c r="M4" t="n">
-        <v>200301000</v>
+        <v>178819000</v>
       </c>
       <c r="N4" t="n">
-        <v>1477000</v>
+        <v>774000</v>
       </c>
       <c r="O4" t="n">
-        <v>-301883896</v>
+        <v>-127818658</v>
       </c>
       <c r="P4" t="n">
-        <v>-1121566000</v>
+        <v>-236690000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1586695000</v>
+        <v>693716000</v>
       </c>
       <c r="R4" t="n">
         <v>114527925</v>
@@ -1007,91 +1009,89 @@
         <v>114527925</v>
       </c>
       <c r="T4" t="n">
-        <v>-9.792</v>
+        <v>-2.984</v>
       </c>
       <c r="U4" t="n">
-        <v>-9.792</v>
+        <v>-2.068</v>
       </c>
       <c r="V4" t="n">
-        <v>-1121566000</v>
+        <v>-236690000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1121566000</v>
+        <v>-236690000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1121566000</v>
+        <v>-236690000</v>
       </c>
       <c r="Z4" t="n">
-        <v>132536000</v>
+        <v>238446000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1254102000</v>
+        <v>-475136000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1254102000</v>
+        <v>-475136000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5605000</v>
+        <v>-8537000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1259707000</v>
+        <v>-483673000</v>
       </c>
       <c r="AE4" t="n">
-        <v>7776000</v>
+        <v>5884000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-830485000</v>
+        <v>43982000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-6577000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>173111000</v>
-      </c>
+        <v>-648911000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>837062000</v>
+        <v>453813000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-198824000</v>
+        <v>-178045000</v>
       </c>
       <c r="AK4" t="n">
-        <v>200301000</v>
+        <v>178819000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1477000</v>
+        <v>774000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-254837000</v>
+        <v>-378134000</v>
       </c>
       <c r="AN4" t="n">
-        <v>386359000</v>
+        <v>297801000</v>
       </c>
       <c r="AO4" t="n">
-        <v>173111000</v>
+        <v>29722000</v>
       </c>
       <c r="AP4" t="n">
-        <v>240190000</v>
+        <v>269411000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>34377000</v>
+        <v>4728000</v>
       </c>
       <c r="AR4" t="n">
-        <v>205813000</v>
+        <v>264683000</v>
       </c>
       <c r="AS4" t="n">
-        <v>131522000</v>
+        <v>-80333000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1200336000</v>
+        <v>395915000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1331858000</v>
+        <v>315582000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1331858000</v>
+        <v>315582000</v>
       </c>
     </row>
   </sheetData>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>114527921</v>
@@ -1461,46 +1461,46 @@
         <v>114527921</v>
       </c>
       <c r="D2" t="n">
-        <v>1644294000</v>
+        <v>2044110000</v>
       </c>
       <c r="E2" t="n">
-        <v>1710893000</v>
+        <v>2152288000</v>
       </c>
       <c r="F2" t="n">
-        <v>597708000</v>
+        <v>1678526000</v>
       </c>
       <c r="G2" t="n">
-        <v>2617778000</v>
+        <v>4494157000</v>
       </c>
       <c r="H2" t="n">
-        <v>-847136000</v>
+        <v>-1881426000</v>
       </c>
       <c r="I2" t="n">
-        <v>597708000</v>
+        <v>1678526000</v>
       </c>
       <c r="J2" t="n">
-        <v>5359000</v>
+        <v>6214000</v>
       </c>
       <c r="K2" t="n">
-        <v>912244000</v>
+        <v>2348083000</v>
       </c>
       <c r="L2" t="n">
-        <v>1848391000</v>
+        <v>2348083000</v>
       </c>
       <c r="M2" t="n">
-        <v>630130000</v>
+        <v>2464019000</v>
       </c>
       <c r="N2" t="n">
-        <v>-282114000</v>
+        <v>115936000</v>
       </c>
       <c r="O2" t="n">
-        <v>912244000</v>
+        <v>2348083000</v>
       </c>
       <c r="P2" t="n">
-        <v>19155000</v>
+        <v>45309000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-464596000</v>
+        <v>741446000</v>
       </c>
       <c r="R2" t="n">
         <v>1357882000</v>
@@ -1512,143 +1512,147 @@
         <v>101419000</v>
       </c>
       <c r="U2" t="n">
-        <v>2592283000</v>
+        <v>3446442000</v>
       </c>
       <c r="V2" t="n">
-        <v>1167676000</v>
+        <v>304696000</v>
       </c>
       <c r="W2" t="n">
-        <v>22074000</v>
+        <v>48789000</v>
       </c>
       <c r="X2" t="n">
-        <v>66881000</v>
+        <v>75018000</v>
       </c>
       <c r="Y2" t="n">
-        <v>940636000</v>
+        <v>5823000</v>
       </c>
       <c r="Z2" t="n">
-        <v>4489000</v>
+        <v>5823000</v>
       </c>
       <c r="AA2" t="n">
-        <v>936147000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1424607000</v>
+        <v>3141746000</v>
       </c>
       <c r="AC2" t="n">
-        <v>770257000</v>
+        <v>2146465000</v>
       </c>
       <c r="AD2" t="n">
-        <v>870000</v>
+        <v>391000</v>
       </c>
       <c r="AE2" t="n">
-        <v>769387000</v>
+        <v>2146074000</v>
       </c>
       <c r="AF2" t="n">
-        <v>122512000</v>
+        <v>189978000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2974000</v>
+        <v>9171000</v>
       </c>
       <c r="AH2" t="n">
-        <v>119538000</v>
+        <v>180807000</v>
       </c>
       <c r="AI2" t="n">
-        <v>3222413000</v>
+        <v>5910461000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2644942000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>4650141000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
       <c r="AL2" t="n">
-        <v>89014000</v>
+        <v>106055000</v>
       </c>
       <c r="AM2" t="n">
-        <v>314536000</v>
+        <v>669557000</v>
       </c>
       <c r="AN2" t="n">
-        <v>314536000</v>
+        <v>518441000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>151116000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2241392000</v>
+        <v>3874529000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1626809000</v>
+        <v>-1545630000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3868201000</v>
+        <v>5420159000</v>
       </c>
       <c r="AS2" t="n">
-        <v>72725000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>113650000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5642000</v>
+      </c>
       <c r="AU2" t="n">
-        <v>1784496000</v>
+        <v>2171329000</v>
       </c>
       <c r="AV2" t="n">
-        <v>16203000</v>
+        <v>18700000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1475481000</v>
+        <v>2534010000</v>
       </c>
       <c r="AX2" t="n">
-        <v>519296000</v>
+        <v>582470000</v>
       </c>
       <c r="AY2" t="n">
-        <v>577471000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>115365000</v>
-      </c>
+        <v>1260320000</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>66000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>10564000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>370176000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>122652000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-1114000</v>
-      </c>
+        <v>357926000</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
-        <v>48335000</v>
+        <v>165653000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2521000</v>
+        <v>1766000</v>
       </c>
       <c r="BG2" t="n">
-        <v>72910000</v>
+        <v>190507000</v>
       </c>
       <c r="BH2" t="n">
-        <v>274491000</v>
+        <v>26314000</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2930000</v>
+        <v>389470000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-221266000</v>
+        <v>-352620000</v>
       </c>
       <c r="BL2" t="n">
-        <v>224196000</v>
+        <v>742090000</v>
       </c>
       <c r="BM2" t="n">
-        <v>61967000</v>
+        <v>105870000</v>
       </c>
       <c r="BN2" t="n">
-        <v>727000</v>
+        <v>3906000</v>
       </c>
       <c r="BO2" t="n">
-        <v>61240000</v>
-      </c>
-      <c r="BP2" t="inlineStr"/>
+        <v>101964000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ2" t="n">
-        <v>61240000</v>
+        <v>101964000</v>
       </c>
     </row>
     <row r="3">
@@ -1858,7 +1862,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>114527921</v>
@@ -1867,46 +1871,46 @@
         <v>114527921</v>
       </c>
       <c r="D4" t="n">
-        <v>2044110000</v>
+        <v>1644294000</v>
       </c>
       <c r="E4" t="n">
-        <v>2152288000</v>
+        <v>1710893000</v>
       </c>
       <c r="F4" t="n">
-        <v>1678526000</v>
+        <v>597708000</v>
       </c>
       <c r="G4" t="n">
-        <v>4494157000</v>
+        <v>2617778000</v>
       </c>
       <c r="H4" t="n">
-        <v>-1881426000</v>
+        <v>-847136000</v>
       </c>
       <c r="I4" t="n">
-        <v>1678526000</v>
+        <v>597708000</v>
       </c>
       <c r="J4" t="n">
-        <v>6214000</v>
+        <v>5359000</v>
       </c>
       <c r="K4" t="n">
-        <v>2348083000</v>
+        <v>912244000</v>
       </c>
       <c r="L4" t="n">
-        <v>2348083000</v>
+        <v>1848391000</v>
       </c>
       <c r="M4" t="n">
-        <v>2464019000</v>
+        <v>630130000</v>
       </c>
       <c r="N4" t="n">
-        <v>115936000</v>
+        <v>-282114000</v>
       </c>
       <c r="O4" t="n">
-        <v>2348083000</v>
+        <v>912244000</v>
       </c>
       <c r="P4" t="n">
-        <v>45309000</v>
+        <v>19155000</v>
       </c>
       <c r="Q4" t="n">
-        <v>741446000</v>
+        <v>-464596000</v>
       </c>
       <c r="R4" t="n">
         <v>1357882000</v>
@@ -1918,147 +1922,143 @@
         <v>101419000</v>
       </c>
       <c r="U4" t="n">
-        <v>3446442000</v>
+        <v>2592283000</v>
       </c>
       <c r="V4" t="n">
-        <v>304696000</v>
+        <v>1167676000</v>
       </c>
       <c r="W4" t="n">
-        <v>48789000</v>
+        <v>22074000</v>
       </c>
       <c r="X4" t="n">
-        <v>75018000</v>
+        <v>66881000</v>
       </c>
       <c r="Y4" t="n">
-        <v>5823000</v>
+        <v>940636000</v>
       </c>
       <c r="Z4" t="n">
-        <v>5823000</v>
+        <v>4489000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>936147000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3141746000</v>
+        <v>1424607000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2146465000</v>
+        <v>770257000</v>
       </c>
       <c r="AD4" t="n">
-        <v>391000</v>
+        <v>870000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2146074000</v>
+        <v>769387000</v>
       </c>
       <c r="AF4" t="n">
-        <v>189978000</v>
+        <v>122512000</v>
       </c>
       <c r="AG4" t="n">
-        <v>9171000</v>
+        <v>2974000</v>
       </c>
       <c r="AH4" t="n">
-        <v>180807000</v>
+        <v>119538000</v>
       </c>
       <c r="AI4" t="n">
-        <v>5910461000</v>
+        <v>3222413000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4650141000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
+        <v>2644942000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>106055000</v>
+        <v>89014000</v>
       </c>
       <c r="AM4" t="n">
-        <v>669557000</v>
+        <v>314536000</v>
       </c>
       <c r="AN4" t="n">
-        <v>518441000</v>
+        <v>314536000</v>
       </c>
       <c r="AO4" t="n">
-        <v>151116000</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>3874529000</v>
+        <v>2241392000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1545630000</v>
+        <v>-1626809000</v>
       </c>
       <c r="AR4" t="n">
-        <v>5420159000</v>
+        <v>3868201000</v>
       </c>
       <c r="AS4" t="n">
-        <v>113650000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5642000</v>
-      </c>
+        <v>72725000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>2171329000</v>
+        <v>1784496000</v>
       </c>
       <c r="AV4" t="n">
-        <v>18700000</v>
+        <v>16203000</v>
       </c>
       <c r="AW4" t="n">
-        <v>2534010000</v>
+        <v>1475481000</v>
       </c>
       <c r="AX4" t="n">
-        <v>582470000</v>
+        <v>519296000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1260320000</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
+        <v>577471000</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>115365000</v>
+      </c>
       <c r="BA4" t="n">
-        <v>10564000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>370176000</v>
-      </c>
+        <v>66000</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>357926000</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
+        <v>122652000</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-1114000</v>
+      </c>
       <c r="BE4" t="n">
-        <v>165653000</v>
+        <v>48335000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1766000</v>
+        <v>2521000</v>
       </c>
       <c r="BG4" t="n">
-        <v>190507000</v>
+        <v>72910000</v>
       </c>
       <c r="BH4" t="n">
-        <v>26314000</v>
+        <v>274491000</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>389470000</v>
+        <v>2930000</v>
       </c>
       <c r="BK4" t="n">
-        <v>-352620000</v>
+        <v>-221266000</v>
       </c>
       <c r="BL4" t="n">
-        <v>742090000</v>
+        <v>224196000</v>
       </c>
       <c r="BM4" t="n">
-        <v>105870000</v>
+        <v>61967000</v>
       </c>
       <c r="BN4" t="n">
-        <v>3906000</v>
+        <v>727000</v>
       </c>
       <c r="BO4" t="n">
-        <v>101964000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
+        <v>61240000</v>
+      </c>
+      <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="n">
-        <v>101964000</v>
+        <v>61240000</v>
       </c>
     </row>
   </sheetData>
@@ -2299,137 +2299,135 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-38997000</v>
+        <v>-36388000</v>
       </c>
       <c r="C2" t="n">
-        <v>-1099000</v>
+        <v>-11502000</v>
       </c>
       <c r="D2" t="n">
-        <v>12750000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8811000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-28596000</v>
+        <v>-239609000</v>
       </c>
       <c r="G2" t="n">
-        <v>61240000</v>
+        <v>101964000</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>76602000</v>
+        <v>157417000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1967000</v>
+        <v>6650000</v>
       </c>
       <c r="K2" t="n">
-        <v>-13395000</v>
+        <v>-62103000</v>
       </c>
       <c r="L2" t="n">
-        <v>10102000</v>
+        <v>-41904000</v>
       </c>
       <c r="M2" t="n">
-        <v>-8994000</v>
+        <v>-29441000</v>
       </c>
       <c r="N2" t="n">
-        <v>8811000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8811000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>11651000</v>
+        <v>-11502000</v>
       </c>
       <c r="Q2" t="n">
-        <v>11651000</v>
+        <v>-11502000</v>
       </c>
       <c r="R2" t="n">
-        <v>-1099000</v>
+        <v>-11502000</v>
       </c>
       <c r="S2" t="n">
-        <v>12750000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-13096000</v>
+        <v>-223420000</v>
       </c>
       <c r="U2" t="n">
-        <v>774000</v>
+        <v>1477000</v>
       </c>
       <c r="V2" t="n">
-        <v>9523000</v>
+        <v>6517000</v>
       </c>
       <c r="W2" t="n">
-        <v>9523000</v>
+        <v>6517000</v>
       </c>
       <c r="X2" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-23488000</v>
+        <v>-231414000</v>
       </c>
       <c r="AA2" t="n">
-        <v>5108000</v>
+        <v>8195000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-28596000</v>
+        <v>-239609000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-10401000</v>
+        <v>203221000</v>
       </c>
       <c r="AD2" t="n">
-        <v>4250000</v>
+        <v>-17746000</v>
       </c>
       <c r="AE2" t="n">
-        <v>124033000</v>
+        <v>58586000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2564000</v>
+        <v>-116944000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1419000</v>
+        <v>-75806000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7201000</v>
+        <v>89514000</v>
       </c>
       <c r="AI2" t="n">
-        <v>93125000</v>
+        <v>198479000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22562000</v>
+        <v>-36657000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-471464000</v>
+        <v>198824000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1639000</v>
+        <v>6756000</v>
       </c>
       <c r="AM2" t="n">
-        <v>11611000</v>
+        <v>173111000</v>
       </c>
       <c r="AN2" t="n">
-        <v>219459000</v>
+        <v>220093000</v>
       </c>
       <c r="AO2" t="n">
-        <v>219459000</v>
+        <v>220093000</v>
       </c>
       <c r="AP2" t="n">
-        <v>963000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-23603000</v>
-      </c>
+        <v>-7261000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>134000</v>
+        <v>-6577000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-483673000</v>
+        <v>-1259707000</v>
       </c>
     </row>
     <row r="3">
@@ -2571,135 +2569,137 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-36388000</v>
+        <v>-38997000</v>
       </c>
       <c r="C4" t="n">
-        <v>-11502000</v>
+        <v>-1099000</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>12750000</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>8811000</v>
       </c>
       <c r="F4" t="n">
-        <v>-239609000</v>
+        <v>-28596000</v>
       </c>
       <c r="G4" t="n">
-        <v>101964000</v>
+        <v>61240000</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>157417000</v>
+        <v>76602000</v>
       </c>
       <c r="J4" t="n">
-        <v>6650000</v>
+        <v>-1967000</v>
       </c>
       <c r="K4" t="n">
-        <v>-62103000</v>
+        <v>-13395000</v>
       </c>
       <c r="L4" t="n">
-        <v>-41904000</v>
+        <v>10102000</v>
       </c>
       <c r="M4" t="n">
-        <v>-29441000</v>
+        <v>-8994000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8811000</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>8811000</v>
       </c>
       <c r="P4" t="n">
-        <v>-11502000</v>
+        <v>11651000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-11502000</v>
+        <v>11651000</v>
       </c>
       <c r="R4" t="n">
-        <v>-11502000</v>
+        <v>-1099000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>12750000</v>
       </c>
       <c r="T4" t="n">
-        <v>-223420000</v>
+        <v>-13096000</v>
       </c>
       <c r="U4" t="n">
-        <v>1477000</v>
+        <v>774000</v>
       </c>
       <c r="V4" t="n">
-        <v>6517000</v>
+        <v>9523000</v>
       </c>
       <c r="W4" t="n">
-        <v>6517000</v>
+        <v>9523000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-231414000</v>
+        <v>-23488000</v>
       </c>
       <c r="AA4" t="n">
-        <v>8195000</v>
+        <v>5108000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-239609000</v>
+        <v>-28596000</v>
       </c>
       <c r="AC4" t="n">
-        <v>203221000</v>
+        <v>-10401000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-17746000</v>
+        <v>4250000</v>
       </c>
       <c r="AE4" t="n">
-        <v>58586000</v>
+        <v>124033000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-116944000</v>
+        <v>2564000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-75806000</v>
+        <v>-1419000</v>
       </c>
       <c r="AH4" t="n">
-        <v>89514000</v>
+        <v>7201000</v>
       </c>
       <c r="AI4" t="n">
-        <v>198479000</v>
+        <v>93125000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-36657000</v>
+        <v>22562000</v>
       </c>
       <c r="AK4" t="n">
-        <v>198824000</v>
+        <v>-471464000</v>
       </c>
       <c r="AL4" t="n">
-        <v>6756000</v>
+        <v>1639000</v>
       </c>
       <c r="AM4" t="n">
-        <v>173111000</v>
+        <v>11611000</v>
       </c>
       <c r="AN4" t="n">
-        <v>220093000</v>
+        <v>219459000</v>
       </c>
       <c r="AO4" t="n">
-        <v>220093000</v>
+        <v>219459000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-7261000</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>963000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-23603000</v>
+      </c>
       <c r="AR4" t="n">
-        <v>-6577000</v>
+        <v>134000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1259707000</v>
+        <v>-483673000</v>
       </c>
     </row>
   </sheetData>
@@ -3249,187 +3249,187 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
@@ -3570,7 +3570,7 @@
         <v>2.07</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.661</v>
+        <v>-0.639</v>
       </c>
       <c r="AH2" t="n">
         <v>182750</v>
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.52</v>
@@ -3814,59 +3814,59 @@
         </is>
       </c>
       <c r="DC2" t="n">
+        <v>-10.052907</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DE2" t="n">
         <v>-0.018999994</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>0.17 - 0.171</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0</v>
-      </c>
       <c r="DH2" t="n">
         <v>0</v>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="inlineStr">
         <is>
           <t>0.17 - 0.171</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DL2" t="n">
         <v>-0.001000002</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="DM2" t="n">
         <v>-0.005847965</v>
       </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
         <v>1725028434</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DP2" t="n">
         <v>1725028434</v>
       </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
+      <c r="DQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
         <v>-1.94</v>
       </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
       <c r="DS2" t="n">
         <v>0</v>
       </c>
@@ -3874,79 +3874,79 @@
         <v>0</v>
       </c>
       <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
         <v>15</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="DX2" t="n">
         <v>15</v>
       </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>SUNSHINE</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Century Sunshine Group Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="inlineStr">
         <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="DY2" t="n">
-        <v>-10.052907</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1166405400000</v>
+      </c>
+      <c r="EE2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EB2" t="n">
+      <c r="EF2" t="n">
         <v>1743405814</v>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>finmb_20579564</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="EG2" t="n">
+      <c r="EK2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1166405400000</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>SUNSHINE</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>Century Sunshine Group Holdings Limited</t>
-        </is>
+      <c r="EM2" t="b">
+        <v>0</v>
       </c>
       <c r="EN2" t="inlineStr"/>
     </row>
